--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104568_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104568_W13.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0812</v>
+        <v>5.5868</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7421</v>
+        <v>4.3041</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3392</v>
+        <v>1.2827</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7945</v>
+        <v>0.8015</v>
       </c>
       <c r="H2" t="n">
-        <v>0.352</v>
+        <v>0.3559</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4425</v>
+        <v>0.4455</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0538</v>
+        <v>2.0337</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3204</v>
+        <v>2.3097</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2593</v>
+        <v>-1.2323</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9684</v>
+        <v>-1.9538</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5816</v>
+        <v>1.0812</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3176</v>
+        <v>0.9125</v>
       </c>
       <c r="U2" t="n">
-        <v>0.264</v>
+        <v>0.1688</v>
       </c>
       <c r="V2" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8037</v>
+        <v>4.8898</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1544</v>
+        <v>3.3018</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6492</v>
+        <v>1.588</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1959</v>
+        <v>0.1937</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0302</v>
+        <v>-1.0338</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2262</v>
+        <v>1.2275</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0953</v>
+        <v>2.0709</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4187</v>
+        <v>0.403</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8993</v>
+        <v>-1.8772</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4489</v>
+        <v>-1.4367</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0293</v>
+        <v>1.0603</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5383</v>
+        <v>0.6454</v>
       </c>
       <c r="U3" t="n">
-        <v>0.509</v>
+        <v>0.4149</v>
       </c>
       <c r="V3" t="n">
-        <v>2.9566</v>
+        <v>2.9529</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7876</v>
+        <v>2.9191</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5553</v>
+        <v>3.289</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2323</v>
+        <v>-0.37</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1636</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-1.9562</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0639</v>
+        <v>3.8161</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0337</v>
+        <v>2.6621</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6407</v>
+        <v>-0.376</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6744</v>
+        <v>3.0381</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1299</v>
+        <v>-0.8022</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-1.5802</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6105</v>
+        <v>0.778</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0438</v>
+        <v>0.742</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8158</v>
+        <v>0.6756</v>
       </c>
       <c r="U4" t="n">
-        <v>0.228</v>
+        <v>0.0664</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1757</v>
+        <v>2.5809</v>
       </c>
       <c r="E5" t="n">
-        <v>1.893</v>
+        <v>1.1394</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2827</v>
+        <v>1.4415</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8556</v>
+        <v>-0.1529</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0258</v>
+        <v>-0.095</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1702</v>
+        <v>-0.0578</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.0402</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9391</v>
+        <v>0.6378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1866</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.103</v>
+        <v>-0.1127</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0867</v>
+        <v>-0.7328</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9837</v>
+        <v>0.6201</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7779</v>
+        <v>1.8232</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5263</v>
+        <v>1.4072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2516</v>
+        <v>0.416</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1448</v>
+        <v>2.2291</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8208</v>
+        <v>1.9876</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.676</v>
+        <v>0.2415</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8613</v>
+        <v>-0.8544</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9611</v>
+        <v>-2.033</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8223</v>
+        <v>1.1787</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6838</v>
+        <v>-0.7693</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3708</v>
+        <v>-0.9555</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0546</v>
+        <v>0.1862</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8225</v>
+        <v>-0.0851</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5903</v>
+        <v>-1.0775</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7678</v>
+        <v>0.9925</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.036</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1785</v>
+        <v>0.6478</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2144</v>
+        <v>0.1884</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>1.792</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>2.3367</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7632</v>
+        <v>1.7859</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8472</v>
+        <v>1.0624</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.084</v>
+        <v>0.7235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1557</v>
+        <v>-0.8878</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1184</v>
+        <v>-1.9613</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0373</v>
+        <v>1.0735</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5745</v>
+        <v>0.4287</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2441</v>
+        <v>-0.3522</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3304</v>
+        <v>0.7809</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4188</v>
+        <v>-1.3164</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1257</v>
+        <v>-1.6091</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2931</v>
+        <v>0.2926</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5395</v>
+        <v>1.8314</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4729</v>
+        <v>1.1377</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0665</v>
+        <v>0.6937</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.387</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2643</v>
+        <v>0.3144</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0639</v>
+        <v>2.3671</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3282</v>
+        <v>-2.0527</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.358</v>
+        <v>0.1523</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.4381</v>
+        <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>0.0372</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7392</v>
+        <v>2.5466</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.4855</v>
+        <v>2.2268</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7463</v>
+        <v>0.3198</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6188</v>
+        <v>-2.3943</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9525</v>
+        <v>-2.1117</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6663</v>
+        <v>-0.2826</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>3.0326</v>
+        <v>1.0938</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2593</v>
+        <v>1.0285</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7733</v>
+        <v>0.0653</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3214</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6429</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0283</v>
+        <v>-0.7654</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.68</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.1485</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8703</v>
+        <v>-5.3743</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9551</v>
+        <v>-5.4641</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0848</v>
+        <v>0.0898</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4744</v>
+        <v>-2.78</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.333</v>
+        <v>-3.5248</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8074</v>
+        <v>0.7447</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3447</v>
+        <v>-2.5943</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6221</v>
+        <v>-1.9394</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2773</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>2.2763</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0027</v>
+        <v>2.0171</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6593</v>
+        <v>1.4628</v>
       </c>
       <c r="U9" t="n">
-        <v>0.662</v>
+        <v>0.5543</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3856</v>
+        <v>0.3155</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0.6311</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7071</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1511</v>
+        <v>-1.9879</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3199</v>
+        <v>-1.1685</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8313</v>
+        <v>-0.8194</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1415</v>
+        <v>-4.1479</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4329</v>
+        <v>-2.4299</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7087</v>
+        <v>-1.7179</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1287</v>
+        <v>-1.1655</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2282</v>
+        <v>0.2133</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3569</v>
+        <v>-1.3789</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0128</v>
+        <v>-2.9824</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6611</v>
+        <v>-2.6433</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4441</v>
+        <v>1.6152</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0506</v>
+        <v>1.2537</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3935</v>
+        <v>0.3616</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8411</v>
+        <v>17.5527</v>
       </c>
       <c r="E11" t="n">
-        <v>14.949</v>
+        <v>15.3691</v>
       </c>
       <c r="F11" t="n">
-        <v>1.892</v>
+        <v>2.1836</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.381599999999999</v>
+        <v>-8.409800000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.4724</v>
+        <v>-14.5023</v>
       </c>
       <c r="I11" t="n">
-        <v>6.090699999999999</v>
+        <v>6.0926</v>
       </c>
       <c r="J11" t="n">
-        <v>5.2277</v>
+        <v>4.987</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7236999999999993</v>
+        <v>0.5820999999999998</v>
       </c>
       <c r="L11" t="n">
-        <v>4.503900000000002</v>
+        <v>4.4049</v>
       </c>
       <c r="M11" t="n">
-        <v>-13.6091</v>
+        <v>-13.3969</v>
       </c>
       <c r="N11" t="n">
-        <v>-15.1961</v>
+        <v>-15.0845</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5869</v>
+        <v>1.6876</v>
       </c>
       <c r="P11" t="n">
-        <v>5.6709</v>
+        <v>5.6909</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.2074</v>
+        <v>-10.2433</v>
       </c>
       <c r="R11" t="n">
-        <v>15.8784</v>
+        <v>15.9341</v>
       </c>
       <c r="S11" t="n">
-        <v>11.3569</v>
+        <v>12.1004</v>
       </c>
       <c r="T11" t="n">
-        <v>8.423400000000001</v>
+        <v>9.171199999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>2.9335</v>
+        <v>2.9294</v>
       </c>
       <c r="V11" t="n">
-        <v>8.194899999999999</v>
+        <v>8.171000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>11.5055</v>
+        <v>11.4544</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3104</v>
+        <v>-3.2833</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6725</v>
+        <v>3.9777</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8288</v>
+        <v>4.207</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1563</v>
+        <v>-0.2293</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7151</v>
+        <v>2.7098</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1819</v>
+        <v>2.1718</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5331</v>
+        <v>0.538</v>
       </c>
       <c r="J12" t="n">
-        <v>4.0094</v>
+        <v>3.9858</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3004</v>
+        <v>3.2783</v>
       </c>
       <c r="L12" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2944</v>
+        <v>-1.2759</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5434</v>
+        <v>0.8629</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0858</v>
+        <v>0.4991</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4576</v>
+        <v>0.3637</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1775</v>
+        <v>1.5382</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6515</v>
+        <v>3.5993</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.474</v>
+        <v>-2.0611</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3542</v>
+        <v>2.3443</v>
       </c>
       <c r="H13" t="n">
-        <v>3.743</v>
+        <v>3.7451</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3888</v>
+        <v>-1.4008</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7893</v>
+        <v>3.7461</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1387</v>
+        <v>4.1196</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3494</v>
+        <v>-0.3735</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4352</v>
+        <v>-1.4018</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3957</v>
+        <v>-0.3745</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5642</v>
+        <v>-1.1915</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2571</v>
+        <v>-0.2559</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3072</v>
+        <v>-0.9356</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0963</v>
+        <v>0.1777</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.276</v>
+        <v>-0.183</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1797</v>
+        <v>0.3607</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3191</v>
+        <v>1.3226</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2308</v>
+        <v>2.2343</v>
       </c>
       <c r="I14" t="n">
         <v>-0.9116</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3931</v>
+        <v>1.376</v>
       </c>
       <c r="K14" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.074</v>
+        <v>-0.0533</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9618</v>
+        <v>-0.6897</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2662</v>
+        <v>-0.1111</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4855</v>
+        <v>-0.2154</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1391</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3463</v>
+        <v>0.5865</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1891</v>
+        <v>0.4801</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3463</v>
+        <v>1.3468</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1573</v>
+        <v>-0.8667</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2901</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.9308</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6407</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1891</v>
+        <v>0.19</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3463</v>
+        <v>0.416</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1573</v>
+        <v>-0.226</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2964</v>
+        <v>-0.0126</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1391</v>
+        <v>-0.1116</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1573</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4873</v>
+        <v>-0.4841</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0232</v>
+        <v>-0.1394</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5359</v>
+        <v>-0.3447</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4717</v>
+        <v>-0.1868</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3433</v>
+        <v>-0.3447</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8716</v>
+        <v>0.1579</v>
       </c>
       <c r="J16" t="n">
-        <v>0.298</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9351</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6371</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1737</v>
+        <v>-0.1868</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4082</v>
+        <v>-0.3447</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>0.1579</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2786</v>
+        <v>-0.2973</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3478</v>
+        <v>-0.1394</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0692</v>
+        <v>-0.1579</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4046</v>
+        <v>-1.6727</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4185</v>
+        <v>-1.3949</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8231</v>
+        <v>-0.2779</v>
       </c>
       <c r="G17" t="n">
-        <v>1.093</v>
+        <v>-1.5765</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5138</v>
+        <v>-0.9448</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4207</v>
+        <v>-0.6317</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6706</v>
+        <v>-1.562</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7982</v>
+        <v>-0.7724</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1276</v>
+        <v>-0.7896</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5776</v>
+        <v>-0.0144</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2844</v>
+        <v>-0.1724</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2931</v>
+        <v>0.1579</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7292</v>
+        <v>0.0615</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0162</v>
+        <v>0.1672</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.287</v>
+        <v>-0.1057</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.639</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.639</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.938</v>
+        <v>-1.9978</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.625</v>
+        <v>-0.3271</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.313</v>
+        <v>-1.6707</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5713</v>
+        <v>1.0823</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9422</v>
+        <v>2.5049</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6291</v>
+        <v>-1.4227</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5554</v>
+        <v>1.6383</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.769</v>
+        <v>2.7784</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7864</v>
+        <v>-1.1401</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0159</v>
+        <v>-0.556</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1732</v>
+        <v>-0.2734</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>-0.2826</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.206</v>
+        <v>0.1476</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>0.311</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1364</v>
+        <v>-0.1634</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1598</v>
+        <v>-2.4482</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3218</v>
+        <v>-0.5795</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.838</v>
+        <v>-1.8687</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1646</v>
+        <v>-0.157</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5204</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3652</v>
+        <v>0.3634</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7911</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0244</v>
+        <v>-0.0312</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9557</v>
+        <v>-0.9296</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9687</v>
+        <v>-1.2716</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9899</v>
+        <v>-1.0576</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2253</v>
+        <v>-2.8374</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.194</v>
+        <v>-0.9508</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0313</v>
+        <v>-1.8866</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4573</v>
+        <v>0.7718</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4732</v>
+        <v>-0.1668</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0159</v>
+        <v>0.9386</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2085</v>
+        <v>1.5278</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4995</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.709</v>
+        <v>1.5935</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2488</v>
+        <v>-0.756</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9737</v>
+        <v>-0.1011</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7249</v>
+        <v>-0.6549</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.4066</v>
+        <v>-1.066</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0434</v>
+        <v>-0.2023</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3631</v>
+        <v>-0.8637</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.5029</v>
+        <v>-1.405</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.278</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4488</v>
+        <v>-3.1893</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.282</v>
+        <v>-0.1013</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1669</v>
+        <v>-3.088</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7653</v>
+        <v>2.4717</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1703</v>
+        <v>2.4756</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9356</v>
+        <v>-0.0039</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5429</v>
+        <v>2.1931</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0591</v>
+        <v>1.4856</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6019</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7776</v>
+        <v>0.2785</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1113</v>
+        <v>0.99</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6663</v>
+        <v>-0.7114</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6659</v>
+        <v>-2.391</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>-0.9271</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1094</v>
+        <v>-1.4639</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4141</v>
+        <v>-3.4976</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4141</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3761</v>
+        <v>-3.7507</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8961</v>
+        <v>-2.6752</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.48</v>
+        <v>-1.0754</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6511</v>
+        <v>-0.6383</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8656</v>
+        <v>0.8782</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5167</v>
+        <v>-1.5164</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7881</v>
+        <v>-0.7981</v>
       </c>
       <c r="K22" t="n">
-        <v>0.71</v>
+        <v>0.7067</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M22" t="n">
-        <v>0.137</v>
+        <v>0.1598</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.4716</v>
+        <v>-1.8652</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9739</v>
+        <v>-0.7389</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4977</v>
+        <v>-1.1262</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0693</v>
+        <v>-4.3743</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0338</v>
+        <v>-2.8369</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0355</v>
+        <v>-1.5375</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2181</v>
+        <v>-0.2143</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1094</v>
+        <v>1.1223</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3275</v>
+        <v>-1.3366</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2499</v>
+        <v>0.2271</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9697</v>
+        <v>0.9653</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.468</v>
+        <v>-0.4414</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8097</v>
+        <v>-2.1113</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9739</v>
+        <v>-0.7389</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8358</v>
+        <v>-1.3724</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.841</v>
+        <v>-15.2763</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.892200000000002</v>
+        <v>-2.1837</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.9488</v>
+        <v>-13.0927</v>
       </c>
       <c r="G24" t="n">
-        <v>8.381500000000001</v>
+        <v>8.409700000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>14.4725</v>
+        <v>14.5023</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.0907</v>
+        <v>-6.092499999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>13.6093</v>
+        <v>13.3969</v>
       </c>
       <c r="K24" t="n">
-        <v>15.1961</v>
+        <v>15.0846</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5868</v>
+        <v>-1.6877</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.228</v>
+        <v>-4.9869</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7238</v>
+        <v>-0.5819999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.504</v>
+        <v>-4.404800000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.671</v>
+        <v>-5.691000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-15.8785</v>
+        <v>-15.9345</v>
       </c>
       <c r="R24" t="n">
-        <v>10.2076</v>
+        <v>10.2436</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.3569</v>
+        <v>-9.824199999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.9337</v>
+        <v>-2.9294</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.4232</v>
+        <v>-6.8947</v>
       </c>
       <c r="V24" t="n">
-        <v>-8.195</v>
+        <v>-8.1709</v>
       </c>
       <c r="W24" t="n">
-        <v>3.3104</v>
+        <v>3.283399999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-11.5054</v>
+        <v>-11.4544</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104568_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104568_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,7 @@
       <c r="X11" t="n">
         <v>-3.2833</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1458,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104568_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-11.4544</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
